--- a/testcase.xlsx
+++ b/testcase.xlsx
@@ -27,18 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Audio File</t>
   </si>
   <si>
-    <t>2.wav</t>
+    <t>1.wav</t>
   </si>
   <si>
-    <t>3.wav</t>
-  </si>
-  <si>
-    <t>6.wav</t>
+    <t>1_D.wav</t>
   </si>
 </sst>
 </file>
@@ -973,8 +970,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -991,11 +988,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
